--- a/data/derived_data/2_RarefyData/Dataset_1/ps_16S_filt_Dataset_1bis_tax_table.xlsx
+++ b/data/derived_data/2_RarefyData/Dataset_1/ps_16S_filt_Dataset_1bis_tax_table.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="45">
   <si>
     <t xml:space="preserve"/>
   </si>
@@ -38,12 +38,33 @@
     <t xml:space="preserve">Species</t>
   </si>
   <si>
+    <t xml:space="preserve">Cluster_10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bacteria</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bacillota</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bacilli</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lactobacillales</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lactobacillaceae</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fructilactobacillus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unknown</t>
+  </si>
+  <si>
     <t xml:space="preserve">Cluster_11</t>
   </si>
   <si>
-    <t xml:space="preserve">Bacteria</t>
-  </si>
-  <si>
     <t xml:space="preserve">Pseudomonadota</t>
   </si>
   <si>
@@ -59,9 +80,6 @@
     <t xml:space="preserve">Gluconobacter</t>
   </si>
   <si>
-    <t xml:space="preserve">Unknown</t>
-  </si>
-  <si>
     <t xml:space="preserve">Cluster_20</t>
   </si>
   <si>
@@ -72,12 +90,6 @@
   </si>
   <si>
     <t xml:space="preserve">Cluster_23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bacillota</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bacilli</t>
   </si>
   <si>
     <t xml:space="preserve">Bacillales</t>
@@ -523,48 +535,48 @@
         <v>9</v>
       </c>
       <c r="C3" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="D3" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="E3" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F3" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="G3" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="H3" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" t="s">
         <v>19</v>
       </c>
-      <c r="B4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4" t="s">
+      <c r="F4" t="s">
         <v>20</v>
       </c>
-      <c r="D4" t="s">
-        <v>21</v>
-      </c>
-      <c r="E4" t="s">
-        <v>22</v>
-      </c>
-      <c r="F4" t="s">
+      <c r="G4" t="s">
         <v>23</v>
       </c>
-      <c r="G4" t="s">
+      <c r="H4" t="s">
         <v>24</v>
-      </c>
-      <c r="H4" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="5">
@@ -578,16 +590,16 @@
         <v>10</v>
       </c>
       <c r="D5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" t="s">
         <v>26</v>
       </c>
-      <c r="E5" t="s">
+      <c r="F5" t="s">
         <v>27</v>
       </c>
-      <c r="F5" t="s">
+      <c r="G5" t="s">
         <v>28</v>
-      </c>
-      <c r="G5" t="s">
-        <v>29</v>
       </c>
       <c r="H5" t="s">
         <v>15</v>
@@ -595,16 +607,16 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
+        <v>29</v>
+      </c>
+      <c r="B6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D6" t="s">
         <v>30</v>
-      </c>
-      <c r="B6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C6" t="s">
-        <v>10</v>
-      </c>
-      <c r="D6" t="s">
-        <v>26</v>
       </c>
       <c r="E6" t="s">
         <v>31</v>
@@ -627,19 +639,19 @@
         <v>9</v>
       </c>
       <c r="C7" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D7" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="E7" t="s">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="F7" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H7" t="s">
         <v>15</v>
@@ -647,7 +659,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B8" t="s">
         <v>9</v>
@@ -659,68 +671,94 @@
         <v>11</v>
       </c>
       <c r="E8" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="F8" t="s">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="G8" t="s">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="H8" t="s">
-        <v>38</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B9" t="s">
         <v>9</v>
       </c>
       <c r="C9" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="D9" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="E9" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F9" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="G9" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="H9" t="s">
-        <v>15</v>
+        <v>42</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B10" t="s">
         <v>9</v>
       </c>
       <c r="C10" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="D10" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="E10" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F10" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="G10" t="s">
+        <v>23</v>
+      </c>
+      <c r="H10" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>44</v>
+      </c>
+      <c r="B11" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" t="s">
         <v>17</v>
       </c>
-      <c r="H10" t="s">
+      <c r="D11" t="s">
         <v>18</v>
+      </c>
+      <c r="E11" t="s">
+        <v>19</v>
+      </c>
+      <c r="F11" t="s">
+        <v>20</v>
+      </c>
+      <c r="G11" t="s">
+        <v>23</v>
+      </c>
+      <c r="H11" t="s">
+        <v>24</v>
       </c>
     </row>
   </sheetData>
